--- a/Design/Excel/GameHot/Datas/Buqi/BuqiRefinement.xlsx
+++ b/Design/Excel/GameHot/Datas/Buqi/BuqiRefinement.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -501,41 +501,92 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cooldown -15%; each active use creates 1 noise.</t>
+          <t>cooldown -15%; each active use creates 1 overload.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>复写</t>
+          <t>激化</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>first active use repeats at 50% effect once per battle.</t>
+          <t>cooldown +20%; non-opening effects +30%.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>复写</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>first active use repeats at 50% effect once per battle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
           <t>A-04</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>可靠</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>immune to enemy delay and ignores friendly haste.</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>immune to enemy slow and ignores friendly haste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A-05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>稳流</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>attack/shield -15%; overload gained by this item -1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A-06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>超载</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>battle start gains 3 overload; attack/shield +35%.</t>
         </is>
       </c>
     </row>

--- a/Design/Excel/GameHot/Datas/Buqi/BuqiRefinement.xlsx
+++ b/Design/Excel/GameHot/Datas/Buqi/BuqiRefinement.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiRefinement" sheetId="1" r:id="R3d83f98d0a344207"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiRefinement" sheetId="1" r:id="R1dc78d47d94c4dc0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,159 +334,117 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RefinementId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DisplayName</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Summary</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>RefinementId</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>DisplayName</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>Summary</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
+      <x:c r="A2" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">refinement id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">display name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">summary</x:t>
-        </x:is>
+      <x:c r="A3" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>refinement id</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>display name</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>summary</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A-01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">加急</x:t>
-        </x:is>
+      <x:c r="A4"/>
+      <x:c r="B4" t="str">
+        <x:v>A-01</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>快速改造</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>冷却缩短 15%；每次主动使用增加 1 点失衡。</x:v>
+        <x:v>冷却缩短 15%；每次主动使用增加 1 点过载。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">激化</x:t>
-        </x:is>
+      <x:c r="A5"/>
+      <x:c r="B5" t="str">
+        <x:v>A-02</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>强效改造</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>冷却延长 20%；非开战效果提高 30%。</x:v>
+        <x:v>冷却延长 20%；非开场效果提高 30%。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A-03</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复写</x:t>
-        </x:is>
+      <x:c r="A6"/>
+      <x:c r="B6" t="str">
+        <x:v>A-03</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>首次重复触发</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>每场战斗首次主动使用时，以 50% 效果额外结算一次。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="B7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A-04</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">可靠</x:t>
-        </x:is>
+      <x:c r="A7"/>
+      <x:c r="B7" t="str">
+        <x:v>A-04</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>稳定改造</x:v>
       </x:c>
       <x:c r="D7" t="str">
         <x:v>免疫敌方减速，但不受友方加速。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="B8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A-05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">稳流</x:t>
-        </x:is>
+      <x:c r="A8"/>
+      <x:c r="B8" t="str">
+        <x:v>A-05</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>低负载改造</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>伤害与护体降低 15%；本器物造成的失衡减少 1 点。</x:v>
+        <x:v>伤害与护盾降低 15%；本装备造成的过载减少 1 点。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="B9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A-06</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">超载</x:t>
-        </x:is>
+      <x:c r="A9"/>
+      <x:c r="B9" t="str">
+        <x:v>A-06</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>高风险强化</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>开战增加 3 点失衡；伤害与护体提高 35%。</x:v>
+        <x:v>开场增加 3 点过载；伤害与护盾提高 35%。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
